--- a/S_数据表/SkillBuff_Template.xlsx
+++ b/S_数据表/SkillBuff_Template.xlsx
@@ -618,7 +618,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="668">
   <si>
     <t>技能ID</t>
   </si>
@@ -1302,7 +1302,7 @@
     <t>眩晕2秒</t>
   </si>
   <si>
-    <t>裂地击减速状态</t>
+    <t>风影击减速状态</t>
   </si>
   <si>
     <t>移动速度减少20%,持续3秒</t>
@@ -1410,130 +1410,133 @@
     <t>11,2,0</t>
   </si>
   <si>
+    <t>Eff_Buff_ShiXue_2</t>
+  </si>
+  <si>
+    <t>流血状态</t>
+  </si>
+  <si>
+    <t>旋风斩恢复1</t>
+  </si>
+  <si>
+    <t>旋风斩回血</t>
+  </si>
+  <si>
+    <t>旋风斩恢复2</t>
+  </si>
+  <si>
+    <t>坚韧状态回血</t>
+  </si>
+  <si>
+    <t>Eff_Buff_3</t>
+  </si>
+  <si>
+    <t>攻击反弹</t>
+  </si>
+  <si>
+    <t>151,2,3</t>
+  </si>
+  <si>
+    <t>魔法反弹</t>
+  </si>
+  <si>
+    <t>152,2,3</t>
+  </si>
+  <si>
+    <t>11,2,3</t>
+  </si>
+  <si>
+    <t>11,2,0.25</t>
+  </si>
+  <si>
+    <t>物防状态</t>
+  </si>
+  <si>
+    <t>17,2,0.25</t>
+  </si>
+  <si>
+    <t>魔防状态</t>
+  </si>
+  <si>
+    <t>20,2,0.25</t>
+  </si>
+  <si>
+    <t>宠物技能:恢复光环</t>
+  </si>
+  <si>
+    <t>Regeneration Aura</t>
+  </si>
+  <si>
+    <t>90040210,90041210</t>
+  </si>
+  <si>
+    <t>Di</t>
+  </si>
+  <si>
+    <t>Eff_GuangHuan_1</t>
+  </si>
+  <si>
+    <t>提升附近全部己方单位每5秒额外恢复当前最大血量2%</t>
+  </si>
+  <si>
+    <t>Regeneration Aura：Extra Recovery 1% Max hp /5s</t>
+  </si>
+  <si>
+    <t>90040211,90041211</t>
+  </si>
+  <si>
+    <t>宠物技能:攻击光环</t>
+  </si>
+  <si>
+    <t>Enraging Aura</t>
+  </si>
+  <si>
+    <t>90040220,90041220</t>
+  </si>
+  <si>
+    <t>Eff_GuangHuan_3</t>
+  </si>
+  <si>
+    <t>提升附近全部己方单位5%攻击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enraging Aura：Enchanced All Companion Attack 5 % </t>
+  </si>
+  <si>
+    <t>90040221,90041221</t>
+  </si>
+  <si>
+    <t>宠物技能:移动光环</t>
+  </si>
+  <si>
+    <t>Speed Aura</t>
+  </si>
+  <si>
+    <t>35,2,0.05</t>
+  </si>
+  <si>
+    <t>90040230,90041230</t>
+  </si>
+  <si>
+    <t>Eff_GuangHuan_2</t>
+  </si>
+  <si>
+    <t>提升附近全部己方单位5%移动速度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed Aura：Enchanced All Companion Speed 55 % </t>
+  </si>
+  <si>
+    <t>90040231,90041231</t>
+  </si>
+  <si>
+    <t>移动状态</t>
+  </si>
+  <si>
+    <t>16,2,0.25</t>
+  </si>
+  <si>
     <t>Eff_Buff_ShiXue</t>
-  </si>
-  <si>
-    <t>流血状态</t>
-  </si>
-  <si>
-    <t>旋风斩恢复1</t>
-  </si>
-  <si>
-    <t>旋风斩回血</t>
-  </si>
-  <si>
-    <t>旋风斩恢复2</t>
-  </si>
-  <si>
-    <t>坚韧状态回血</t>
-  </si>
-  <si>
-    <t>Eff_Buff_3</t>
-  </si>
-  <si>
-    <t>攻击反弹</t>
-  </si>
-  <si>
-    <t>151,2,3</t>
-  </si>
-  <si>
-    <t>魔法反弹</t>
-  </si>
-  <si>
-    <t>152,2,3</t>
-  </si>
-  <si>
-    <t>11,2,3</t>
-  </si>
-  <si>
-    <t>11,2,0.25</t>
-  </si>
-  <si>
-    <t>物防状态</t>
-  </si>
-  <si>
-    <t>17,2,0.25</t>
-  </si>
-  <si>
-    <t>魔防状态</t>
-  </si>
-  <si>
-    <t>20,2,0.25</t>
-  </si>
-  <si>
-    <t>宠物技能:恢复光环</t>
-  </si>
-  <si>
-    <t>Regeneration Aura</t>
-  </si>
-  <si>
-    <t>90040210,90041210</t>
-  </si>
-  <si>
-    <t>Di</t>
-  </si>
-  <si>
-    <t>Eff_GuangHuan_1</t>
-  </si>
-  <si>
-    <t>提升附近全部己方单位每5秒额外恢复当前最大血量2%</t>
-  </si>
-  <si>
-    <t>Regeneration Aura：Extra Recovery 1% Max hp /5s</t>
-  </si>
-  <si>
-    <t>90040211,90041211</t>
-  </si>
-  <si>
-    <t>宠物技能:攻击光环</t>
-  </si>
-  <si>
-    <t>Enraging Aura</t>
-  </si>
-  <si>
-    <t>90040220,90041220</t>
-  </si>
-  <si>
-    <t>Eff_GuangHuan_3</t>
-  </si>
-  <si>
-    <t>提升附近全部己方单位5%攻击</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enraging Aura：Enchanced All Companion Attack 5 % </t>
-  </si>
-  <si>
-    <t>90040221,90041221</t>
-  </si>
-  <si>
-    <t>宠物技能:移动光环</t>
-  </si>
-  <si>
-    <t>Speed Aura</t>
-  </si>
-  <si>
-    <t>35,2,0.05</t>
-  </si>
-  <si>
-    <t>90040230,90041230</t>
-  </si>
-  <si>
-    <t>Eff_GuangHuan_2</t>
-  </si>
-  <si>
-    <t>提升附近全部己方单位5%移动速度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed Aura：Enchanced All Companion Speed 55 % </t>
-  </si>
-  <si>
-    <t>90040231,90041231</t>
-  </si>
-  <si>
-    <t>移动状态</t>
-  </si>
-  <si>
-    <t>16,2,0.25</t>
   </si>
   <si>
     <t>17,2,0.5</t>
@@ -4285,7 +4288,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4477,22 +4480,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -4574,9 +4562,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="方正书宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="方正书宋_GBK"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4595,19 +4594,8 @@
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="方正书宋_GBK"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="方正书宋_GBK"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="84">
+  <fills count="68">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4940,42 +4928,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399884029663991"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5043,66 +4995,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399914548173467"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5481,58 +5373,76 @@
     <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5553,101 +5463,83 @@
     <xf numFmtId="0" fontId="26" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="68" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="69" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="70" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="72" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="73" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="74" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="75" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="76" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="77" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="78" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="79" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="80" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="81" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="82" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="83" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="83" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6350,7 +6242,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{5B75B1A3-2D17-4B01-8188-5EF60091C010}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{A3ED300F-653F-4B65-829F-6B446B7C29CF}">
       <tableStyleElement type="wholeTable" dxfId="23"/>
       <tableStyleElement type="headerRow" dxfId="22"/>
     </tableStyle>
@@ -16909,7 +16801,7 @@
         <v>46</v>
       </c>
       <c r="T158" s="28" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="U158" s="22" t="s">
         <v>51</v>
@@ -17135,7 +17027,7 @@
         <v>1</v>
       </c>
       <c r="J162" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K162" s="19">
         <v>0</v>
@@ -17199,7 +17091,7 @@
         <v>1</v>
       </c>
       <c r="J163" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K163" s="19">
         <v>0</v>
@@ -17263,7 +17155,7 @@
         <v>1</v>
       </c>
       <c r="J164" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K164" s="19">
         <v>0</v>
@@ -17305,7 +17197,7 @@
         <v>90041112</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C165" s="18"/>
       <c r="D165" s="19">
@@ -17327,7 +17219,7 @@
         <v>2</v>
       </c>
       <c r="J165" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K165" s="19">
         <v>0</v>
@@ -17433,10 +17325,10 @@
         <v>90041210</v>
       </c>
       <c r="B167" s="27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D167" s="28">
         <v>1</v>
@@ -17490,10 +17382,10 @@
         <v>236</v>
       </c>
       <c r="U167" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="V167" s="20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="168" s="10" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -17501,7 +17393,7 @@
         <v>90041211</v>
       </c>
       <c r="B168" s="27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C168" s="18"/>
       <c r="D168" s="28">
@@ -17556,7 +17448,7 @@
         <v>236</v>
       </c>
       <c r="U168" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="V168" s="20"/>
     </row>
@@ -17565,10 +17457,10 @@
         <v>90041220</v>
       </c>
       <c r="B169" s="27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C169" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D169" s="28">
         <v>1</v>
@@ -17622,10 +17514,10 @@
         <v>243</v>
       </c>
       <c r="U169" s="22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="V169" s="20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="170" s="10" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -17633,7 +17525,7 @@
         <v>90041221</v>
       </c>
       <c r="B170" s="27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C170" s="18"/>
       <c r="D170" s="28">
@@ -17688,7 +17580,7 @@
         <v>243</v>
       </c>
       <c r="U170" s="22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="V170" s="20"/>
     </row>
@@ -17697,10 +17589,10 @@
         <v>90041230</v>
       </c>
       <c r="B171" s="27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D171" s="28">
         <v>1</v>
@@ -17721,7 +17613,7 @@
         <v>1</v>
       </c>
       <c r="J171" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K171" s="28">
         <v>2</v>
@@ -17754,10 +17646,10 @@
         <v>251</v>
       </c>
       <c r="U171" s="22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="V171" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="172" s="10" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -17765,7 +17657,7 @@
         <v>90041231</v>
       </c>
       <c r="B172" s="27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C172" s="18"/>
       <c r="D172" s="28">
@@ -17787,7 +17679,7 @@
         <v>1</v>
       </c>
       <c r="J172" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K172" s="28">
         <v>2</v>
@@ -17820,7 +17712,7 @@
         <v>251</v>
       </c>
       <c r="U172" s="22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="V172" s="20"/>
     </row>
@@ -17915,7 +17807,7 @@
         <v>1</v>
       </c>
       <c r="J174" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K174" s="19">
         <v>0</v>
@@ -17945,7 +17837,7 @@
         <v>46</v>
       </c>
       <c r="T174" s="19" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="U174" s="22" t="s">
         <v>51</v>
@@ -17960,7 +17852,7 @@
         <v>228</v>
       </c>
       <c r="C175" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D175" s="19">
         <v>1</v>
@@ -17981,7 +17873,7 @@
         <v>1</v>
       </c>
       <c r="J175" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K175" s="19">
         <v>0</v>
@@ -18014,10 +17906,10 @@
         <v>114</v>
       </c>
       <c r="U175" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V175" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="176" ht="20.1" customHeight="1" spans="1:22">
@@ -18047,7 +17939,7 @@
         <v>1</v>
       </c>
       <c r="J176" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K176" s="19">
         <v>0</v>
@@ -18092,7 +17984,7 @@
         <v>228</v>
       </c>
       <c r="C177" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D177" s="19">
         <v>1</v>
@@ -18113,7 +18005,7 @@
         <v>1</v>
       </c>
       <c r="J177" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K177" s="19">
         <v>0</v>
@@ -18146,10 +18038,10 @@
         <v>114</v>
       </c>
       <c r="U177" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V177" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="178" ht="20.1" customHeight="1" spans="1:22">
@@ -18160,7 +18052,7 @@
         <v>228</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D178" s="19">
         <v>1</v>
@@ -18181,7 +18073,7 @@
         <v>1</v>
       </c>
       <c r="J178" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K178" s="19">
         <v>0</v>
@@ -18214,10 +18106,10 @@
         <v>114</v>
       </c>
       <c r="U178" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V178" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="179" ht="20.1" customHeight="1" spans="1:22">
@@ -18228,7 +18120,7 @@
         <v>228</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D179" s="19">
         <v>1</v>
@@ -18249,7 +18141,7 @@
         <v>1</v>
       </c>
       <c r="J179" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K179" s="19">
         <v>0</v>
@@ -18282,10 +18174,10 @@
         <v>114</v>
       </c>
       <c r="U179" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V179" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="180" ht="20.1" customHeight="1" spans="1:22">
@@ -18315,7 +18207,7 @@
         <v>1</v>
       </c>
       <c r="J180" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K180" s="19">
         <v>0</v>
@@ -18379,7 +18271,7 @@
         <v>1</v>
       </c>
       <c r="J181" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K181" s="19">
         <v>1</v>
@@ -18421,7 +18313,7 @@
         <v>90050210</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C182" s="18"/>
       <c r="D182" s="19">
@@ -18485,7 +18377,7 @@
         <v>90060001</v>
       </c>
       <c r="B183" s="27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C183" s="18"/>
       <c r="D183" s="28">
@@ -18507,7 +18399,7 @@
         <v>1</v>
       </c>
       <c r="J183" s="28" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K183" s="28">
         <v>0</v>
@@ -18540,7 +18432,7 @@
         <v>168</v>
       </c>
       <c r="U183" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V183" s="20"/>
     </row>
@@ -18549,7 +18441,7 @@
         <v>90060002</v>
       </c>
       <c r="B184" s="27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C184" s="18"/>
       <c r="D184" s="28">
@@ -18571,7 +18463,7 @@
         <v>1</v>
       </c>
       <c r="J184" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K184" s="28">
         <v>0</v>
@@ -18604,7 +18496,7 @@
         <v>168</v>
       </c>
       <c r="U184" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V184" s="20"/>
     </row>
@@ -18613,7 +18505,7 @@
         <v>90060004</v>
       </c>
       <c r="B185" s="27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C185" s="18"/>
       <c r="D185" s="28">
@@ -18635,7 +18527,7 @@
         <v>1</v>
       </c>
       <c r="J185" s="28" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K185" s="28">
         <v>0</v>
@@ -18668,7 +18560,7 @@
         <v>168</v>
       </c>
       <c r="U185" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V185" s="20"/>
     </row>
@@ -18741,7 +18633,7 @@
         <v>90060006</v>
       </c>
       <c r="B187" s="27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C187" s="18"/>
       <c r="D187" s="28">
@@ -18763,7 +18655,7 @@
         <v>1</v>
       </c>
       <c r="J187" s="28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K187" s="28">
         <v>0</v>
@@ -18796,7 +18688,7 @@
         <v>168</v>
       </c>
       <c r="U187" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V187" s="20"/>
     </row>
@@ -18805,7 +18697,7 @@
         <v>90060007</v>
       </c>
       <c r="B188" s="27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C188" s="18"/>
       <c r="D188" s="28">
@@ -18827,7 +18719,7 @@
         <v>1</v>
       </c>
       <c r="J188" s="28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K188" s="28">
         <v>0</v>
@@ -18860,7 +18752,7 @@
         <v>168</v>
       </c>
       <c r="U188" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V188" s="20"/>
     </row>
@@ -18933,7 +18825,7 @@
         <v>90060009</v>
       </c>
       <c r="B190" s="27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C190" s="18"/>
       <c r="D190" s="28">
@@ -18955,7 +18847,7 @@
         <v>1</v>
       </c>
       <c r="J190" s="28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K190" s="28">
         <v>0</v>
@@ -18988,7 +18880,7 @@
         <v>168</v>
       </c>
       <c r="U190" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V190" s="20"/>
     </row>
@@ -18997,7 +18889,7 @@
         <v>90060011</v>
       </c>
       <c r="B191" s="27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C191" s="18"/>
       <c r="D191" s="28">
@@ -19019,7 +18911,7 @@
         <v>1</v>
       </c>
       <c r="J191" s="28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K191" s="28">
         <v>0</v>
@@ -19052,7 +18944,7 @@
         <v>168</v>
       </c>
       <c r="U191" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V191" s="20"/>
     </row>
@@ -19061,7 +18953,7 @@
         <v>90060012</v>
       </c>
       <c r="B192" s="27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C192" s="18"/>
       <c r="D192" s="28">
@@ -19083,7 +18975,7 @@
         <v>1</v>
       </c>
       <c r="J192" s="28" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K192" s="28">
         <v>0</v>
@@ -19116,7 +19008,7 @@
         <v>168</v>
       </c>
       <c r="U192" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V192" s="20"/>
     </row>
@@ -19125,7 +19017,7 @@
         <v>90060013</v>
       </c>
       <c r="B193" s="27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C193" s="18"/>
       <c r="D193" s="28">
@@ -19147,7 +19039,7 @@
         <v>1</v>
       </c>
       <c r="J193" s="28" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K193" s="28">
         <v>0</v>
@@ -19180,7 +19072,7 @@
         <v>168</v>
       </c>
       <c r="U193" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V193" s="20"/>
     </row>
@@ -19211,7 +19103,7 @@
         <v>1</v>
       </c>
       <c r="J194" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K194" s="19">
         <v>0</v>
@@ -19253,7 +19145,7 @@
         <v>90060017</v>
       </c>
       <c r="B195" s="27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C195" s="18"/>
       <c r="D195" s="28">
@@ -19308,7 +19200,7 @@
         <v>0</v>
       </c>
       <c r="U195" s="39" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="V195" s="20"/>
     </row>
@@ -19339,7 +19231,7 @@
         <v>1</v>
       </c>
       <c r="J196" s="19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K196" s="19">
         <v>0</v>
@@ -19381,7 +19273,7 @@
         <v>90060019</v>
       </c>
       <c r="B197" s="27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C197" s="18"/>
       <c r="D197" s="28">
@@ -19403,7 +19295,7 @@
         <v>1</v>
       </c>
       <c r="J197" s="28" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K197" s="28">
         <v>0</v>
@@ -19436,7 +19328,7 @@
         <v>168</v>
       </c>
       <c r="U197" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="V197" s="20"/>
     </row>
@@ -19509,10 +19401,10 @@
         <v>90090021</v>
       </c>
       <c r="B199" s="27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C199" s="18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D199" s="28">
         <v>1</v>
@@ -19533,7 +19425,7 @@
         <v>1</v>
       </c>
       <c r="J199" s="28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K199" s="28">
         <v>0</v>
@@ -19566,10 +19458,10 @@
         <v>168</v>
       </c>
       <c r="U199" s="30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="V199" s="20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="200" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -19577,10 +19469,10 @@
         <v>90090041</v>
       </c>
       <c r="B200" s="27" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C200" s="18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D200" s="28">
         <v>1</v>
@@ -19601,7 +19493,7 @@
         <v>1</v>
       </c>
       <c r="J200" s="28" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K200" s="28">
         <v>0</v>
@@ -19634,10 +19526,10 @@
         <v>0</v>
       </c>
       <c r="U200" s="30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="V200" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="201" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -19645,10 +19537,10 @@
         <v>90090061</v>
       </c>
       <c r="B201" s="27" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C201" s="18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D201" s="28">
         <v>1</v>
@@ -19669,13 +19561,13 @@
         <v>1</v>
       </c>
       <c r="J201" s="28" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K201" s="28">
         <v>0</v>
       </c>
       <c r="L201" s="49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M201" s="28">
         <v>0</v>
@@ -19702,10 +19594,10 @@
         <v>0</v>
       </c>
       <c r="U201" s="30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="V201" s="20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="202" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -19713,10 +19605,10 @@
         <v>90090071</v>
       </c>
       <c r="B202" s="27" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C202" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D202" s="28">
         <v>1</v>
@@ -19737,7 +19629,7 @@
         <v>1</v>
       </c>
       <c r="J202" s="28" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K202" s="28">
         <v>0</v>
@@ -19770,10 +19662,10 @@
         <v>0</v>
       </c>
       <c r="U202" s="30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="V202" s="20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="203" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -19781,10 +19673,10 @@
         <v>90090091</v>
       </c>
       <c r="B203" s="27" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C203" s="18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D203" s="28">
         <v>1</v>
@@ -19805,7 +19697,7 @@
         <v>1</v>
       </c>
       <c r="J203" s="28" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K203" s="28">
         <v>0</v>
@@ -19838,10 +19730,10 @@
         <v>0</v>
       </c>
       <c r="U203" s="30" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="V203" s="20" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="204" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -19849,10 +19741,10 @@
         <v>90090101</v>
       </c>
       <c r="B204" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C204" s="18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D204" s="28">
         <v>1</v>
@@ -19873,7 +19765,7 @@
         <v>1</v>
       </c>
       <c r="J204" s="28" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K204" s="28">
         <v>0</v>
@@ -19906,10 +19798,10 @@
         <v>0</v>
       </c>
       <c r="U204" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V204" s="20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="205" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -19917,10 +19809,10 @@
         <v>90090111</v>
       </c>
       <c r="B205" s="27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C205" s="18" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D205" s="28">
         <v>1</v>
@@ -19941,7 +19833,7 @@
         <v>1</v>
       </c>
       <c r="J205" s="28" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K205" s="28">
         <v>0</v>
@@ -19974,10 +19866,10 @@
         <v>0</v>
       </c>
       <c r="U205" s="30" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="V205" s="20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="206" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -19985,10 +19877,10 @@
         <v>90090121</v>
       </c>
       <c r="B206" s="27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C206" s="18" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D206" s="28">
         <v>1</v>
@@ -20042,10 +19934,10 @@
         <v>0</v>
       </c>
       <c r="U206" s="39" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="V206" s="20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="207" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20053,10 +19945,10 @@
         <v>90090131</v>
       </c>
       <c r="B207" s="27" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C207" s="18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D207" s="28">
         <v>1</v>
@@ -20077,7 +19969,7 @@
         <v>1</v>
       </c>
       <c r="J207" s="28" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K207" s="28">
         <v>0</v>
@@ -20110,10 +20002,10 @@
         <v>0</v>
       </c>
       <c r="U207" s="30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="V207" s="20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="208" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20121,10 +20013,10 @@
         <v>90090141</v>
       </c>
       <c r="B208" s="27" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C208" s="18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D208" s="28">
         <v>1</v>
@@ -20145,7 +20037,7 @@
         <v>1</v>
       </c>
       <c r="J208" s="28" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K208" s="28">
         <v>0</v>
@@ -20178,10 +20070,10 @@
         <v>0</v>
       </c>
       <c r="U208" s="30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="V208" s="20" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="209" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20189,10 +20081,10 @@
         <v>90090151</v>
       </c>
       <c r="B209" s="27" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C209" s="18" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D209" s="28">
         <v>1</v>
@@ -20213,7 +20105,7 @@
         <v>1</v>
       </c>
       <c r="J209" s="28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K209" s="28">
         <v>0</v>
@@ -20246,10 +20138,10 @@
         <v>0</v>
       </c>
       <c r="U209" s="30" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="V209" s="20" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="210" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20257,10 +20149,10 @@
         <v>90090161</v>
       </c>
       <c r="B210" s="27" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C210" s="18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D210" s="28">
         <v>1</v>
@@ -20281,7 +20173,7 @@
         <v>1</v>
       </c>
       <c r="J210" s="28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K210" s="28">
         <v>0</v>
@@ -20314,10 +20206,10 @@
         <v>0</v>
       </c>
       <c r="U210" s="30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="V210" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="211" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20325,10 +20217,10 @@
         <v>90090171</v>
       </c>
       <c r="B211" s="27" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C211" s="18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D211" s="28">
         <v>1</v>
@@ -20349,13 +20241,13 @@
         <v>1</v>
       </c>
       <c r="J211" s="28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K211" s="28">
         <v>2</v>
       </c>
       <c r="L211" s="49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M211" s="28">
         <v>0</v>
@@ -20382,10 +20274,10 @@
         <v>0</v>
       </c>
       <c r="U211" s="30" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="V211" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="212" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20393,10 +20285,10 @@
         <v>90090181</v>
       </c>
       <c r="B212" s="27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C212" s="18" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D212" s="28">
         <v>1</v>
@@ -20417,7 +20309,7 @@
         <v>1</v>
       </c>
       <c r="J212" s="28" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K212" s="28">
         <v>0</v>
@@ -20450,10 +20342,10 @@
         <v>0</v>
       </c>
       <c r="U212" s="30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="V212" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="213" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20461,10 +20353,10 @@
         <v>90090191</v>
       </c>
       <c r="B213" s="27" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C213" s="18" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D213" s="28">
         <v>1</v>
@@ -20485,7 +20377,7 @@
         <v>1</v>
       </c>
       <c r="J213" s="28" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K213" s="28">
         <v>0</v>
@@ -20518,10 +20410,10 @@
         <v>0</v>
       </c>
       <c r="U213" s="30" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="V213" s="20" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="214" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20529,10 +20421,10 @@
         <v>90090201</v>
       </c>
       <c r="B214" s="27" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C214" s="18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D214" s="28">
         <v>1</v>
@@ -20553,7 +20445,7 @@
         <v>1</v>
       </c>
       <c r="J214" s="28" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K214" s="28">
         <v>0</v>
@@ -20586,10 +20478,10 @@
         <v>0</v>
       </c>
       <c r="U214" s="30" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="V214" s="20" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="215" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20597,10 +20489,10 @@
         <v>90090211</v>
       </c>
       <c r="B215" s="27" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C215" s="18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D215" s="28">
         <v>1</v>
@@ -20654,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="U215" s="39" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="V215" s="20" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="216" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20665,10 +20557,10 @@
         <v>90090221</v>
       </c>
       <c r="B216" s="27" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C216" s="18" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D216" s="28">
         <v>1</v>
@@ -20689,13 +20581,13 @@
         <v>1</v>
       </c>
       <c r="J216" s="28" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K216" s="28">
         <v>0</v>
       </c>
       <c r="L216" s="49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M216" s="28">
         <v>0</v>
@@ -20722,10 +20614,10 @@
         <v>0</v>
       </c>
       <c r="U216" s="30" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="V216" s="20" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="217" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20733,7 +20625,7 @@
         <v>91001011</v>
       </c>
       <c r="B217" s="29" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C217" s="18" t="s">
         <v>117</v>
@@ -20790,10 +20682,10 @@
         <v>96</v>
       </c>
       <c r="U217" s="31" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="V217" s="20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="218" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20801,10 +20693,10 @@
         <v>91001031</v>
       </c>
       <c r="B218" s="27" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C218" s="18" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D218" s="28">
         <v>1</v>
@@ -20825,13 +20717,13 @@
         <v>1</v>
       </c>
       <c r="J218" s="28" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K218" s="28">
         <v>2</v>
       </c>
       <c r="L218" s="50" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M218" s="28">
         <v>0</v>
@@ -20858,10 +20750,10 @@
         <v>0</v>
       </c>
       <c r="U218" s="30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="V218" s="20" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="219" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -20893,13 +20785,13 @@
         <v>1</v>
       </c>
       <c r="J219" s="28" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K219" s="28">
         <v>2</v>
       </c>
       <c r="L219" s="50" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M219" s="28">
         <v>0</v>
@@ -20959,13 +20851,13 @@
         <v>1</v>
       </c>
       <c r="J220" s="28" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K220" s="28">
         <v>2</v>
       </c>
       <c r="L220" s="50" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M220" s="28">
         <v>0</v>
@@ -20999,10 +20891,10 @@
         <v>91001061</v>
       </c>
       <c r="B221" s="27" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C221" s="18" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D221" s="28">
         <v>1</v>
@@ -21023,13 +20915,13 @@
         <v>1</v>
       </c>
       <c r="J221" s="28" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K221" s="28">
         <v>2</v>
       </c>
       <c r="L221" s="51" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M221" s="28">
         <v>0</v>
@@ -21056,10 +20948,10 @@
         <v>0</v>
       </c>
       <c r="U221" s="30" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="V221" s="20" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="222" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21067,10 +20959,10 @@
         <v>91001071</v>
       </c>
       <c r="B222" s="27" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C222" s="18" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D222" s="28">
         <v>1</v>
@@ -21091,13 +20983,13 @@
         <v>1</v>
       </c>
       <c r="J222" s="28" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K222" s="28">
         <v>2</v>
       </c>
       <c r="L222" s="51" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M222" s="28">
         <v>0</v>
@@ -21124,10 +21016,10 @@
         <v>0</v>
       </c>
       <c r="U222" s="30" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="V222" s="20" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="223" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21135,10 +21027,10 @@
         <v>91001081</v>
       </c>
       <c r="B223" s="27" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C223" s="18" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D223" s="28">
         <v>1</v>
@@ -21159,13 +21051,13 @@
         <v>1</v>
       </c>
       <c r="J223" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K223" s="28">
         <v>2</v>
       </c>
       <c r="L223" s="51" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M223" s="28">
         <v>0</v>
@@ -21192,10 +21084,10 @@
         <v>0</v>
       </c>
       <c r="U223" s="30" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="V223" s="20" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="224" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21225,13 +21117,13 @@
         <v>1</v>
       </c>
       <c r="J224" s="28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K224" s="28">
         <v>2</v>
       </c>
       <c r="L224" s="51" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M224" s="28">
         <v>0</v>
@@ -21265,10 +21157,10 @@
         <v>91002011</v>
       </c>
       <c r="B225" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D225" s="28">
         <v>1</v>
@@ -21322,10 +21214,10 @@
         <v>96</v>
       </c>
       <c r="U225" s="31" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="V225" s="20" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="226" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21333,10 +21225,10 @@
         <v>91002031</v>
       </c>
       <c r="B226" s="27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C226" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D226" s="28">
         <v>1</v>
@@ -21357,13 +21249,13 @@
         <v>1</v>
       </c>
       <c r="J226" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K226" s="28">
         <v>2</v>
       </c>
       <c r="L226" s="50" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M226" s="28">
         <v>0</v>
@@ -21390,10 +21282,10 @@
         <v>0</v>
       </c>
       <c r="U226" s="30" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="V226" s="20" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="227" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21401,10 +21293,10 @@
         <v>91002041</v>
       </c>
       <c r="B227" s="27" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D227" s="28">
         <v>1</v>
@@ -21425,13 +21317,13 @@
         <v>1</v>
       </c>
       <c r="J227" s="28" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K227" s="28">
         <v>2</v>
       </c>
       <c r="L227" s="50" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M227" s="28">
         <v>0</v>
@@ -21458,10 +21350,10 @@
         <v>0</v>
       </c>
       <c r="U227" s="31" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="V227" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="228" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21491,13 +21383,13 @@
         <v>1</v>
       </c>
       <c r="J228" s="28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K228" s="28">
         <v>2</v>
       </c>
       <c r="L228" s="50" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M228" s="28">
         <v>0</v>
@@ -21531,10 +21423,10 @@
         <v>91002061</v>
       </c>
       <c r="B229" s="27" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C229" s="18" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D229" s="28">
         <v>1</v>
@@ -21555,13 +21447,13 @@
         <v>1</v>
       </c>
       <c r="J229" s="28" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K229" s="28">
         <v>2</v>
       </c>
       <c r="L229" s="51" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M229" s="28">
         <v>0</v>
@@ -21588,10 +21480,10 @@
         <v>0</v>
       </c>
       <c r="U229" s="31" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="V229" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="230" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21599,10 +21491,10 @@
         <v>91002071</v>
       </c>
       <c r="B230" s="27" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C230" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D230" s="28">
         <v>1</v>
@@ -21623,13 +21515,13 @@
         <v>1</v>
       </c>
       <c r="J230" s="28" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K230" s="28">
         <v>2</v>
       </c>
       <c r="L230" s="51" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M230" s="28">
         <v>0</v>
@@ -21656,10 +21548,10 @@
         <v>0</v>
       </c>
       <c r="U230" s="31" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="V230" s="20" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="231" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21667,10 +21559,10 @@
         <v>91002081</v>
       </c>
       <c r="B231" s="27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C231" s="18" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D231" s="28">
         <v>1</v>
@@ -21691,13 +21583,13 @@
         <v>1</v>
       </c>
       <c r="J231" s="28" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K231" s="28">
         <v>2</v>
       </c>
       <c r="L231" s="51" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M231" s="28">
         <v>0</v>
@@ -21724,10 +21616,10 @@
         <v>0</v>
       </c>
       <c r="U231" s="31" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="V231" s="20" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="232" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21757,13 +21649,13 @@
         <v>1</v>
       </c>
       <c r="J232" s="28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K232" s="28">
         <v>2</v>
       </c>
       <c r="L232" s="51" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M232" s="28">
         <v>0</v>
@@ -21797,10 +21689,10 @@
         <v>91003011</v>
       </c>
       <c r="B233" s="29" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C233" s="18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D233" s="28">
         <v>1</v>
@@ -21854,10 +21746,10 @@
         <v>96</v>
       </c>
       <c r="U233" s="31" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="V233" s="20" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="234" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21865,10 +21757,10 @@
         <v>91003031</v>
       </c>
       <c r="B234" s="27" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D234" s="28">
         <v>1</v>
@@ -21889,13 +21781,13 @@
         <v>1</v>
       </c>
       <c r="J234" s="28" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K234" s="28">
         <v>2</v>
       </c>
       <c r="L234" s="50" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M234" s="28">
         <v>0</v>
@@ -21922,10 +21814,10 @@
         <v>0</v>
       </c>
       <c r="U234" s="30" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="V234" s="20" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="235" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -21933,10 +21825,10 @@
         <v>91003041</v>
       </c>
       <c r="B235" s="27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C235" s="18" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D235" s="28">
         <v>1</v>
@@ -21957,13 +21849,13 @@
         <v>1</v>
       </c>
       <c r="J235" s="28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K235" s="28">
         <v>2</v>
       </c>
       <c r="L235" s="50" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M235" s="28">
         <v>0</v>
@@ -21990,10 +21882,10 @@
         <v>0</v>
       </c>
       <c r="U235" s="31" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="V235" s="20" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="236" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22023,13 +21915,13 @@
         <v>1</v>
       </c>
       <c r="J236" s="28" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K236" s="28">
         <v>2</v>
       </c>
       <c r="L236" s="50" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M236" s="28">
         <v>0</v>
@@ -22063,10 +21955,10 @@
         <v>91003061</v>
       </c>
       <c r="B237" s="27" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C237" s="18" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D237" s="28">
         <v>1</v>
@@ -22087,13 +21979,13 @@
         <v>1</v>
       </c>
       <c r="J237" s="28" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K237" s="28">
         <v>2</v>
       </c>
       <c r="L237" s="51" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M237" s="28">
         <v>0</v>
@@ -22120,10 +22012,10 @@
         <v>0</v>
       </c>
       <c r="U237" s="31" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="V237" s="20" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="238" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22131,10 +22023,10 @@
         <v>91003071</v>
       </c>
       <c r="B238" s="27" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C238" s="18" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D238" s="28">
         <v>1</v>
@@ -22155,13 +22047,13 @@
         <v>1</v>
       </c>
       <c r="J238" s="28" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K238" s="28">
         <v>2</v>
       </c>
       <c r="L238" s="51" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M238" s="28">
         <v>0</v>
@@ -22188,10 +22080,10 @@
         <v>0</v>
       </c>
       <c r="U238" s="31" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="V238" s="20" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22199,10 +22091,10 @@
         <v>91003081</v>
       </c>
       <c r="B239" s="27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C239" s="18" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D239" s="28">
         <v>1</v>
@@ -22223,13 +22115,13 @@
         <v>1</v>
       </c>
       <c r="J239" s="28" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K239" s="28">
         <v>2</v>
       </c>
       <c r="L239" s="51" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M239" s="28">
         <v>0</v>
@@ -22256,10 +22148,10 @@
         <v>0</v>
       </c>
       <c r="U239" s="31" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="V239" s="20" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="240" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22289,13 +22181,13 @@
         <v>1</v>
       </c>
       <c r="J240" s="28" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K240" s="28">
         <v>2</v>
       </c>
       <c r="L240" s="51" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M240" s="28">
         <v>0</v>
@@ -22329,10 +22221,10 @@
         <v>91004011</v>
       </c>
       <c r="B241" s="29" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C241" s="18" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D241" s="28">
         <v>1</v>
@@ -22386,10 +22278,10 @@
         <v>96</v>
       </c>
       <c r="U241" s="31" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="V241" s="20" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="242" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22397,10 +22289,10 @@
         <v>91004031</v>
       </c>
       <c r="B242" s="27" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C242" s="18" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D242" s="28">
         <v>1</v>
@@ -22421,13 +22313,13 @@
         <v>1</v>
       </c>
       <c r="J242" s="28" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K242" s="28">
         <v>2</v>
       </c>
       <c r="L242" s="50" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M242" s="28">
         <v>0</v>
@@ -22454,10 +22346,10 @@
         <v>0</v>
       </c>
       <c r="U242" s="30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="V242" s="20" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="243" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22465,10 +22357,10 @@
         <v>91004041</v>
       </c>
       <c r="B243" s="27" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C243" s="18" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D243" s="28">
         <v>1</v>
@@ -22489,13 +22381,13 @@
         <v>1</v>
       </c>
       <c r="J243" s="28" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K243" s="28">
         <v>2</v>
       </c>
       <c r="L243" s="50" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M243" s="28">
         <v>0</v>
@@ -22522,10 +22414,10 @@
         <v>0</v>
       </c>
       <c r="U243" s="31" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="V243" s="20" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="244" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22555,13 +22447,13 @@
         <v>1</v>
       </c>
       <c r="J244" s="28" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K244" s="28">
         <v>2</v>
       </c>
       <c r="L244" s="50" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M244" s="28">
         <v>0</v>
@@ -22595,10 +22487,10 @@
         <v>91004061</v>
       </c>
       <c r="B245" s="27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C245" s="18" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D245" s="28">
         <v>1</v>
@@ -22619,13 +22511,13 @@
         <v>1</v>
       </c>
       <c r="J245" s="28" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K245" s="28">
         <v>2</v>
       </c>
       <c r="L245" s="51" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M245" s="28">
         <v>0</v>
@@ -22652,10 +22544,10 @@
         <v>0</v>
       </c>
       <c r="U245" s="31" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="V245" s="20" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="246" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22663,10 +22555,10 @@
         <v>91004071</v>
       </c>
       <c r="B246" s="27" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D246" s="28">
         <v>1</v>
@@ -22687,13 +22579,13 @@
         <v>1</v>
       </c>
       <c r="J246" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K246" s="28">
         <v>2</v>
       </c>
       <c r="L246" s="51" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M246" s="28">
         <v>0</v>
@@ -22720,10 +22612,10 @@
         <v>0</v>
       </c>
       <c r="U246" s="31" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="V246" s="20" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="247" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22731,10 +22623,10 @@
         <v>91004081</v>
       </c>
       <c r="B247" s="27" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D247" s="28">
         <v>1</v>
@@ -22755,13 +22647,13 @@
         <v>1</v>
       </c>
       <c r="J247" s="28" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K247" s="28">
         <v>2</v>
       </c>
       <c r="L247" s="51" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M247" s="28">
         <v>0</v>
@@ -22788,10 +22680,10 @@
         <v>0</v>
       </c>
       <c r="U247" s="31" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="V247" s="20" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22821,13 +22713,13 @@
         <v>1</v>
       </c>
       <c r="J248" s="28" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K248" s="28">
         <v>2</v>
       </c>
       <c r="L248" s="51" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M248" s="28">
         <v>0</v>
@@ -22861,10 +22753,10 @@
         <v>91005011</v>
       </c>
       <c r="B249" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D249" s="28">
         <v>1</v>
@@ -22918,10 +22810,10 @@
         <v>96</v>
       </c>
       <c r="U249" s="31" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="V249" s="20" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="250" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22929,10 +22821,10 @@
         <v>91005031</v>
       </c>
       <c r="B250" s="27" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C250" s="18" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D250" s="28">
         <v>1</v>
@@ -22953,13 +22845,13 @@
         <v>1</v>
       </c>
       <c r="J250" s="28" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K250" s="28">
         <v>2</v>
       </c>
       <c r="L250" s="50" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M250" s="28">
         <v>0</v>
@@ -22986,10 +22878,10 @@
         <v>0</v>
       </c>
       <c r="U250" s="30" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="V250" s="20" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="251" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -22997,10 +22889,10 @@
         <v>91005041</v>
       </c>
       <c r="B251" s="27" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C251" s="18" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D251" s="28">
         <v>1</v>
@@ -23021,13 +22913,13 @@
         <v>1</v>
       </c>
       <c r="J251" s="28" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K251" s="28">
         <v>2</v>
       </c>
       <c r="L251" s="50" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M251" s="28">
         <v>0</v>
@@ -23054,10 +22946,10 @@
         <v>0</v>
       </c>
       <c r="U251" s="31" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="V251" s="20" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="252" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -23087,13 +22979,13 @@
         <v>1</v>
       </c>
       <c r="J252" s="28" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K252" s="28">
         <v>2</v>
       </c>
       <c r="L252" s="50" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M252" s="28">
         <v>0</v>
@@ -23127,10 +23019,10 @@
         <v>91005061</v>
       </c>
       <c r="B253" s="27" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D253" s="28">
         <v>1</v>
@@ -23151,13 +23043,13 @@
         <v>1</v>
       </c>
       <c r="J253" s="28" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K253" s="28">
         <v>2</v>
       </c>
       <c r="L253" s="51" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M253" s="28">
         <v>0</v>
@@ -23184,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="U253" s="31" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="V253" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="254" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -23195,10 +23087,10 @@
         <v>91005071</v>
       </c>
       <c r="B254" s="27" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D254" s="28">
         <v>1</v>
@@ -23219,13 +23111,13 @@
         <v>1</v>
       </c>
       <c r="J254" s="28" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K254" s="28">
         <v>2</v>
       </c>
       <c r="L254" s="51" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M254" s="28">
         <v>0</v>
@@ -23252,10 +23144,10 @@
         <v>0</v>
       </c>
       <c r="U254" s="31" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="V254" s="20" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="255" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -23263,10 +23155,10 @@
         <v>91005081</v>
       </c>
       <c r="B255" s="27" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C255" s="18" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D255" s="28">
         <v>1</v>
@@ -23287,13 +23179,13 @@
         <v>1</v>
       </c>
       <c r="J255" s="28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K255" s="28">
         <v>2</v>
       </c>
       <c r="L255" s="51" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M255" s="28">
         <v>0</v>
@@ -23320,10 +23212,10 @@
         <v>0</v>
       </c>
       <c r="U255" s="31" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="V255" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="256" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -23353,13 +23245,13 @@
         <v>1</v>
       </c>
       <c r="J256" s="28" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K256" s="28">
         <v>2</v>
       </c>
       <c r="L256" s="51" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M256" s="28">
         <v>0</v>
@@ -23393,10 +23285,10 @@
         <v>91100001</v>
       </c>
       <c r="B257" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C257" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D257" s="28">
         <v>1</v>
@@ -23417,7 +23309,7 @@
         <v>1</v>
       </c>
       <c r="J257" s="28" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K257" s="28">
         <v>1</v>
@@ -23455,10 +23347,10 @@
         <v>91100002</v>
       </c>
       <c r="B258" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C258" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D258" s="28">
         <v>1</v>
@@ -23479,7 +23371,7 @@
         <v>1</v>
       </c>
       <c r="J258" s="28" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K258" s="28">
         <v>1</v>
@@ -23517,10 +23409,10 @@
         <v>91100003</v>
       </c>
       <c r="B259" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C259" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D259" s="28">
         <v>1</v>
@@ -23541,7 +23433,7 @@
         <v>1</v>
       </c>
       <c r="J259" s="28" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K259" s="28">
         <v>1</v>
@@ -23579,10 +23471,10 @@
         <v>91100004</v>
       </c>
       <c r="B260" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C260" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D260" s="28">
         <v>1</v>
@@ -23603,7 +23495,7 @@
         <v>1</v>
       </c>
       <c r="J260" s="28" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K260" s="28">
         <v>1</v>
@@ -23641,10 +23533,10 @@
         <v>91100005</v>
       </c>
       <c r="B261" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C261" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D261" s="28">
         <v>1</v>
@@ -23665,7 +23557,7 @@
         <v>1</v>
       </c>
       <c r="J261" s="28" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K261" s="28">
         <v>1</v>
@@ -23703,10 +23595,10 @@
         <v>91100006</v>
       </c>
       <c r="B262" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D262" s="28">
         <v>1</v>
@@ -23727,7 +23619,7 @@
         <v>1</v>
       </c>
       <c r="J262" s="28" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K262" s="28">
         <v>1</v>
@@ -23765,10 +23657,10 @@
         <v>91100007</v>
       </c>
       <c r="B263" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C263" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D263" s="28">
         <v>1</v>
@@ -23789,7 +23681,7 @@
         <v>1</v>
       </c>
       <c r="J263" s="28" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K263" s="28">
         <v>1</v>
@@ -23827,10 +23719,10 @@
         <v>91100008</v>
       </c>
       <c r="B264" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C264" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D264" s="28">
         <v>1</v>
@@ -23851,7 +23743,7 @@
         <v>1</v>
       </c>
       <c r="J264" s="28" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K264" s="28">
         <v>1</v>
@@ -23889,10 +23781,10 @@
         <v>91100009</v>
       </c>
       <c r="B265" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C265" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D265" s="28">
         <v>1</v>
@@ -23913,7 +23805,7 @@
         <v>1</v>
       </c>
       <c r="J265" s="28" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K265" s="28">
         <v>1</v>
@@ -23951,10 +23843,10 @@
         <v>91100010</v>
       </c>
       <c r="B266" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C266" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D266" s="28">
         <v>1</v>
@@ -23975,7 +23867,7 @@
         <v>1</v>
       </c>
       <c r="J266" s="28" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K266" s="28">
         <v>1</v>
@@ -24013,10 +23905,10 @@
         <v>91100011</v>
       </c>
       <c r="B267" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C267" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D267" s="28">
         <v>1</v>
@@ -24037,7 +23929,7 @@
         <v>1</v>
       </c>
       <c r="J267" s="28" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K267" s="28">
         <v>1</v>
@@ -24075,10 +23967,10 @@
         <v>91100012</v>
       </c>
       <c r="B268" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C268" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D268" s="28">
         <v>1</v>
@@ -24099,7 +23991,7 @@
         <v>1</v>
       </c>
       <c r="J268" s="28" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K268" s="28">
         <v>1</v>
@@ -24137,10 +24029,10 @@
         <v>91100013</v>
       </c>
       <c r="B269" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C269" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D269" s="28">
         <v>1</v>
@@ -24161,7 +24053,7 @@
         <v>1</v>
       </c>
       <c r="J269" s="28" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K269" s="28">
         <v>1</v>
@@ -24199,10 +24091,10 @@
         <v>91100014</v>
       </c>
       <c r="B270" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C270" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D270" s="28">
         <v>1</v>
@@ -24223,7 +24115,7 @@
         <v>1</v>
       </c>
       <c r="J270" s="28" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K270" s="28">
         <v>1</v>
@@ -24261,10 +24153,10 @@
         <v>91100015</v>
       </c>
       <c r="B271" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C271" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D271" s="28">
         <v>1</v>
@@ -24285,7 +24177,7 @@
         <v>1</v>
       </c>
       <c r="J271" s="28" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K271" s="28">
         <v>1</v>
@@ -24345,7 +24237,7 @@
         <v>1</v>
       </c>
       <c r="J272" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K272" s="19">
         <v>0</v>
@@ -24378,7 +24270,7 @@
         <v>114</v>
       </c>
       <c r="U272" s="22" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="V272" s="20"/>
     </row>
@@ -24409,7 +24301,7 @@
         <v>1</v>
       </c>
       <c r="J273" s="19" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K273" s="19">
         <v>0</v>
@@ -24442,7 +24334,7 @@
         <v>114</v>
       </c>
       <c r="U273" s="22" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="V273" s="20"/>
     </row>
@@ -24451,7 +24343,7 @@
         <v>94102001</v>
       </c>
       <c r="B274" s="41" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C274" s="32"/>
       <c r="D274" s="32">
@@ -24506,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="U274" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="275" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -24514,7 +24406,7 @@
         <v>94102002</v>
       </c>
       <c r="B275" s="41" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C275" s="32"/>
       <c r="D275" s="32">
@@ -24569,7 +24461,7 @@
         <v>54</v>
       </c>
       <c r="U275" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="276" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -24577,7 +24469,7 @@
         <v>94103001</v>
       </c>
       <c r="B276" s="41" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C276" s="32"/>
       <c r="D276" s="32">
@@ -24632,7 +24524,7 @@
         <v>54</v>
       </c>
       <c r="U276" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="277" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -24640,7 +24532,7 @@
         <v>94103002</v>
       </c>
       <c r="B277" s="41" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C277" s="32"/>
       <c r="D277" s="32">
@@ -24695,7 +24587,7 @@
         <v>0</v>
       </c>
       <c r="U277" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="278" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -24703,7 +24595,7 @@
         <v>94104001</v>
       </c>
       <c r="B278" s="43" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C278" s="44"/>
       <c r="D278" s="32">
@@ -24758,7 +24650,7 @@
         <v>0</v>
       </c>
       <c r="U278" s="42" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="279" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -24766,7 +24658,7 @@
         <v>94104002</v>
       </c>
       <c r="B279" s="43" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C279" s="44"/>
       <c r="D279" s="32">
@@ -24821,7 +24713,7 @@
         <v>0</v>
       </c>
       <c r="U279" s="42" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="280" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -24884,7 +24776,7 @@
         <v>54</v>
       </c>
       <c r="U280" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="281" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -24892,7 +24784,7 @@
         <v>94105001</v>
       </c>
       <c r="B281" s="41" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C281" s="32"/>
       <c r="D281" s="32">
@@ -24947,7 +24839,7 @@
         <v>0</v>
       </c>
       <c r="U281" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="282" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -24955,7 +24847,7 @@
         <v>94105002</v>
       </c>
       <c r="B282" s="41" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C282" s="32"/>
       <c r="D282" s="32">
@@ -25010,7 +24902,7 @@
         <v>127</v>
       </c>
       <c r="U282" s="42" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="283" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -25081,7 +24973,7 @@
         <v>94106002</v>
       </c>
       <c r="B284" s="41" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C284" s="32"/>
       <c r="D284" s="32">
@@ -25136,7 +25028,7 @@
         <v>54</v>
       </c>
       <c r="U284" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="285" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -25144,7 +25036,7 @@
         <v>94106003</v>
       </c>
       <c r="B285" s="41" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C285" s="32"/>
       <c r="D285" s="32">
@@ -25199,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="U285" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="286" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -25207,7 +25099,7 @@
         <v>94201001</v>
       </c>
       <c r="B286" s="41" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C286" s="32"/>
       <c r="D286" s="32">
@@ -25262,7 +25154,7 @@
         <v>47</v>
       </c>
       <c r="U286" s="42" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="287" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -25270,7 +25162,7 @@
         <v>94202001</v>
       </c>
       <c r="B287" s="41" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C287" s="41"/>
       <c r="D287" s="41">
@@ -25292,7 +25184,7 @@
         <v>2</v>
       </c>
       <c r="J287" s="41" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K287" s="41">
         <v>0</v>
@@ -25333,7 +25225,7 @@
         <v>94202002</v>
       </c>
       <c r="B288" s="41" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C288" s="32"/>
       <c r="D288" s="32">
@@ -25355,7 +25247,7 @@
         <v>1</v>
       </c>
       <c r="J288" s="32" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K288" s="32">
         <v>1</v>
@@ -25388,7 +25280,7 @@
         <v>109</v>
       </c>
       <c r="U288" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="289" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -25396,7 +25288,7 @@
         <v>94203001</v>
       </c>
       <c r="B289" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C289" s="32"/>
       <c r="D289" s="32">
@@ -25451,7 +25343,7 @@
         <v>54</v>
       </c>
       <c r="U289" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="290" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -25459,7 +25351,7 @@
         <v>94203002</v>
       </c>
       <c r="B290" s="41" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C290" s="32"/>
       <c r="D290" s="32">
@@ -25522,7 +25414,7 @@
         <v>94204001</v>
       </c>
       <c r="B291" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C291" s="32"/>
       <c r="D291" s="32">
@@ -25585,7 +25477,7 @@
         <v>94204002</v>
       </c>
       <c r="B292" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C292" s="32"/>
       <c r="D292" s="32">
@@ -25640,7 +25532,7 @@
         <v>54</v>
       </c>
       <c r="U292" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="293" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -25648,7 +25540,7 @@
         <v>94204003</v>
       </c>
       <c r="B293" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C293" s="32"/>
       <c r="D293" s="32">
@@ -25703,7 +25595,7 @@
         <v>54</v>
       </c>
       <c r="U293" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="294" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -25711,7 +25603,7 @@
         <v>94301001</v>
       </c>
       <c r="B294" s="41" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C294" s="32"/>
       <c r="D294" s="32">
@@ -25774,7 +25666,7 @@
         <v>94301002</v>
       </c>
       <c r="B295" s="41" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C295" s="32"/>
       <c r="D295" s="32">
@@ -25829,7 +25721,7 @@
         <v>0</v>
       </c>
       <c r="U295" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="296" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -25837,7 +25729,7 @@
         <v>94301003</v>
       </c>
       <c r="B296" s="41" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C296" s="32"/>
       <c r="D296" s="32">
@@ -25859,7 +25751,7 @@
         <v>1</v>
       </c>
       <c r="J296" s="32" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K296" s="32">
         <v>1</v>
@@ -25892,7 +25784,7 @@
         <v>0</v>
       </c>
       <c r="U296" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="297" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -25900,7 +25792,7 @@
         <v>94302001</v>
       </c>
       <c r="B297" s="41" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C297" s="32"/>
       <c r="D297" s="32">
@@ -25955,7 +25847,7 @@
         <v>54</v>
       </c>
       <c r="U297" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="298" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -25963,7 +25855,7 @@
         <v>94302002</v>
       </c>
       <c r="B298" s="41" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C298" s="32"/>
       <c r="D298" s="32">
@@ -26018,7 +25910,7 @@
         <v>0</v>
       </c>
       <c r="U298" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="299" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26026,7 +25918,7 @@
         <v>94303001</v>
       </c>
       <c r="B299" s="41" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C299" s="32"/>
       <c r="D299" s="32">
@@ -26089,7 +25981,7 @@
         <v>94303002</v>
       </c>
       <c r="B300" s="41" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C300" s="32"/>
       <c r="D300" s="32">
@@ -26144,7 +26036,7 @@
         <v>47</v>
       </c>
       <c r="U300" s="42" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="301" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26152,7 +26044,7 @@
         <v>94303003</v>
       </c>
       <c r="B301" s="41" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C301" s="32"/>
       <c r="D301" s="32">
@@ -26207,7 +26099,7 @@
         <v>0</v>
       </c>
       <c r="U301" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="302" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26215,7 +26107,7 @@
         <v>94304001</v>
       </c>
       <c r="B302" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C302" s="32"/>
       <c r="D302" s="32">
@@ -26278,7 +26170,7 @@
         <v>94304002</v>
       </c>
       <c r="B303" s="41" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C303" s="32"/>
       <c r="D303" s="32">
@@ -26333,7 +26225,7 @@
         <v>47</v>
       </c>
       <c r="U303" s="42" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="304" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26341,7 +26233,7 @@
         <v>94304003</v>
       </c>
       <c r="B304" s="41" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C304" s="32"/>
       <c r="D304" s="32">
@@ -26393,10 +26285,10 @@
         <v>46</v>
       </c>
       <c r="T304" s="32" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="U304" s="42" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="305" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26404,7 +26296,7 @@
         <v>94401001</v>
       </c>
       <c r="B305" s="41" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C305" s="32"/>
       <c r="D305" s="32">
@@ -26426,7 +26318,7 @@
         <v>1</v>
       </c>
       <c r="J305" s="32" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K305" s="32">
         <v>1</v>
@@ -26459,7 +26351,7 @@
         <v>0</v>
       </c>
       <c r="U305" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="306" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26467,7 +26359,7 @@
         <v>94401002</v>
       </c>
       <c r="B306" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C306" s="32"/>
       <c r="D306" s="32">
@@ -26522,7 +26414,7 @@
         <v>54</v>
       </c>
       <c r="U306" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="307" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26530,7 +26422,7 @@
         <v>94402001</v>
       </c>
       <c r="B307" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C307" s="32"/>
       <c r="D307" s="32">
@@ -26585,7 +26477,7 @@
         <v>54</v>
       </c>
       <c r="U307" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="308" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26593,7 +26485,7 @@
         <v>94402002</v>
       </c>
       <c r="B308" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C308" s="32"/>
       <c r="D308" s="32">
@@ -26656,7 +26548,7 @@
         <v>94403001</v>
       </c>
       <c r="B309" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C309" s="32"/>
       <c r="D309" s="32">
@@ -26711,7 +26603,7 @@
         <v>54</v>
       </c>
       <c r="U309" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="310" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26719,7 +26611,7 @@
         <v>94403002</v>
       </c>
       <c r="B310" s="41" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C310" s="32"/>
       <c r="D310" s="32">
@@ -26771,10 +26663,10 @@
         <v>46</v>
       </c>
       <c r="T310" s="32" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="U310" s="42" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="311" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26782,7 +26674,7 @@
         <v>94403003</v>
       </c>
       <c r="B311" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C311" s="32"/>
       <c r="D311" s="32">
@@ -26845,7 +26737,7 @@
         <v>94404001</v>
       </c>
       <c r="B312" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C312" s="32"/>
       <c r="D312" s="32">
@@ -26908,7 +26800,7 @@
         <v>94404002</v>
       </c>
       <c r="B313" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C313" s="32"/>
       <c r="D313" s="32">
@@ -26963,7 +26855,7 @@
         <v>54</v>
       </c>
       <c r="U313" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="314" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -26971,7 +26863,7 @@
         <v>94404003</v>
       </c>
       <c r="B314" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C314" s="32"/>
       <c r="D314" s="32">
@@ -27026,7 +26918,7 @@
         <v>54</v>
       </c>
       <c r="U314" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="315" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27034,7 +26926,7 @@
         <v>94404004</v>
       </c>
       <c r="B315" s="41" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C315" s="32"/>
       <c r="D315" s="32">
@@ -27056,7 +26948,7 @@
         <v>1</v>
       </c>
       <c r="J315" s="32" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K315" s="32">
         <v>1</v>
@@ -27089,7 +26981,7 @@
         <v>0</v>
       </c>
       <c r="U315" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="316" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27097,7 +26989,7 @@
         <v>94501001</v>
       </c>
       <c r="B316" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C316" s="32"/>
       <c r="D316" s="32">
@@ -27152,7 +27044,7 @@
         <v>54</v>
       </c>
       <c r="U316" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="317" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27160,7 +27052,7 @@
         <v>94501002</v>
       </c>
       <c r="B317" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C317" s="32"/>
       <c r="D317" s="32">
@@ -27223,7 +27115,7 @@
         <v>94501003</v>
       </c>
       <c r="B318" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C318" s="32"/>
       <c r="D318" s="32">
@@ -27278,7 +27170,7 @@
         <v>54</v>
       </c>
       <c r="U318" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="319" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27286,7 +27178,7 @@
         <v>94501004</v>
       </c>
       <c r="B319" s="41" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C319" s="41"/>
       <c r="D319" s="41">
@@ -27349,7 +27241,7 @@
         <v>94502001</v>
       </c>
       <c r="B320" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C320" s="32"/>
       <c r="D320" s="32">
@@ -27412,7 +27304,7 @@
         <v>94502002</v>
       </c>
       <c r="B321" s="41" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C321" s="32"/>
       <c r="D321" s="32">
@@ -27467,7 +27359,7 @@
         <v>0</v>
       </c>
       <c r="U321" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="322" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27475,7 +27367,7 @@
         <v>94502003</v>
       </c>
       <c r="B322" s="41" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C322" s="32"/>
       <c r="D322" s="32">
@@ -27530,7 +27422,7 @@
         <v>0</v>
       </c>
       <c r="U322" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="323" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27538,7 +27430,7 @@
         <v>94502004</v>
       </c>
       <c r="B323" s="41" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C323" s="41"/>
       <c r="D323" s="41">
@@ -27601,7 +27493,7 @@
         <v>94502005</v>
       </c>
       <c r="B324" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C324" s="32"/>
       <c r="D324" s="32">
@@ -27656,7 +27548,7 @@
         <v>54</v>
       </c>
       <c r="U324" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="325" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27664,7 +27556,7 @@
         <v>94503001</v>
       </c>
       <c r="B325" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C325" s="32"/>
       <c r="D325" s="32">
@@ -27727,7 +27619,7 @@
         <v>94503002</v>
       </c>
       <c r="B326" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C326" s="32"/>
       <c r="D326" s="32">
@@ -27782,7 +27674,7 @@
         <v>54</v>
       </c>
       <c r="U326" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="327" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27790,7 +27682,7 @@
         <v>94504001</v>
       </c>
       <c r="B327" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C327" s="32"/>
       <c r="D327" s="32">
@@ -27845,7 +27737,7 @@
         <v>54</v>
       </c>
       <c r="U327" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="328" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27853,7 +27745,7 @@
         <v>94504002</v>
       </c>
       <c r="B328" s="41" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C328" s="41"/>
       <c r="D328" s="41">
@@ -27916,7 +27808,7 @@
         <v>94504003</v>
       </c>
       <c r="B329" s="41" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C329" s="32"/>
       <c r="D329" s="32">
@@ -27971,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="U329" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="330" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -27979,7 +27871,7 @@
         <v>94505001</v>
       </c>
       <c r="B330" s="41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C330" s="32"/>
       <c r="D330" s="32">
@@ -28042,7 +27934,7 @@
         <v>94505002</v>
       </c>
       <c r="B331" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C331" s="32"/>
       <c r="D331" s="32">
@@ -28097,7 +27989,7 @@
         <v>54</v>
       </c>
       <c r="U331" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="332" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -28105,7 +27997,7 @@
         <v>94505003</v>
       </c>
       <c r="B332" s="41" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C332" s="32"/>
       <c r="D332" s="32">
@@ -28160,7 +28052,7 @@
         <v>0</v>
       </c>
       <c r="U332" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="333" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -28168,7 +28060,7 @@
         <v>94505004</v>
       </c>
       <c r="B333" s="41" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C333" s="32"/>
       <c r="D333" s="32">
@@ -28223,7 +28115,7 @@
         <v>54</v>
       </c>
       <c r="U333" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="334" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -28231,7 +28123,7 @@
         <v>94505005</v>
       </c>
       <c r="B334" s="41" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C334" s="32"/>
       <c r="D334" s="32">
@@ -28286,7 +28178,7 @@
         <v>0</v>
       </c>
       <c r="U334" s="42" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="335" s="11" customFormat="1" ht="20.1" customHeight="1" spans="1:21">
@@ -28294,7 +28186,7 @@
         <v>94507001</v>
       </c>
       <c r="B335" s="41" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C335" s="32"/>
       <c r="D335" s="32">
@@ -28357,7 +28249,7 @@
         <v>95001001</v>
       </c>
       <c r="B336" s="21" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C336" s="45"/>
       <c r="D336" s="19">
@@ -28379,7 +28271,7 @@
         <v>2</v>
       </c>
       <c r="J336" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K336" s="19">
         <v>0</v>
@@ -28418,7 +28310,7 @@
         <v>95001002</v>
       </c>
       <c r="B337" s="19" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C337" s="19"/>
       <c r="D337" s="19">
@@ -28479,7 +28371,7 @@
         <v>95001003</v>
       </c>
       <c r="B338" s="19" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C338" s="19"/>
       <c r="D338" s="19">
@@ -28532,7 +28424,7 @@
         <v>54</v>
       </c>
       <c r="U338" s="19" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="339" s="10" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
@@ -28540,10 +28432,10 @@
         <v>96000001</v>
       </c>
       <c r="B339" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C339" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D339" s="28">
         <v>1</v>
@@ -28597,10 +28489,10 @@
         <v>0</v>
       </c>
       <c r="U339" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V339" s="19" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="340" ht="20.1" customHeight="1" spans="1:22">
@@ -28608,10 +28500,10 @@
         <v>96000002</v>
       </c>
       <c r="B340" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C340" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D340" s="28">
         <v>1</v>
@@ -28665,10 +28557,10 @@
         <v>0</v>
       </c>
       <c r="U340" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V340" s="19" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="341" ht="20.1" customHeight="1" spans="1:22">
@@ -28676,10 +28568,10 @@
         <v>96000003</v>
       </c>
       <c r="B341" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C341" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D341" s="28">
         <v>1</v>
@@ -28733,10 +28625,10 @@
         <v>0</v>
       </c>
       <c r="U341" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V341" s="19" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="342" ht="20.1" customHeight="1" spans="1:22">
@@ -28744,10 +28636,10 @@
         <v>96000004</v>
       </c>
       <c r="B342" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C342" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D342" s="28">
         <v>1</v>
@@ -28801,10 +28693,10 @@
         <v>0</v>
       </c>
       <c r="U342" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V342" s="19" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="343" ht="20.1" customHeight="1" spans="1:22">
@@ -28812,10 +28704,10 @@
         <v>96000005</v>
       </c>
       <c r="B343" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C343" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D343" s="28">
         <v>1</v>
@@ -28869,10 +28761,10 @@
         <v>0</v>
       </c>
       <c r="U343" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V343" s="19" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="344" ht="20.1" customHeight="1" spans="1:22">
@@ -28880,10 +28772,10 @@
         <v>96000006</v>
       </c>
       <c r="B344" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C344" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D344" s="28">
         <v>1</v>
@@ -28937,10 +28829,10 @@
         <v>0</v>
       </c>
       <c r="U344" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V344" s="19" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="345" ht="20.1" customHeight="1" spans="1:22">
@@ -28948,10 +28840,10 @@
         <v>96000007</v>
       </c>
       <c r="B345" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C345" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D345" s="28">
         <v>1</v>
@@ -29005,10 +28897,10 @@
         <v>0</v>
       </c>
       <c r="U345" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V345" s="19" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="346" ht="20.1" customHeight="1" spans="1:22">
@@ -29016,10 +28908,10 @@
         <v>96000008</v>
       </c>
       <c r="B346" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C346" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D346" s="28">
         <v>1</v>
@@ -29073,10 +28965,10 @@
         <v>0</v>
       </c>
       <c r="U346" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V346" s="19" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="347" ht="20.1" customHeight="1" spans="1:22">
@@ -29084,10 +28976,10 @@
         <v>96000009</v>
       </c>
       <c r="B347" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C347" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D347" s="28">
         <v>1</v>
@@ -29141,10 +29033,10 @@
         <v>0</v>
       </c>
       <c r="U347" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V347" s="19" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="348" ht="20.1" customHeight="1" spans="1:22">
@@ -29152,10 +29044,10 @@
         <v>96000010</v>
       </c>
       <c r="B348" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C348" s="46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D348" s="28">
         <v>1</v>
@@ -29209,10 +29101,10 @@
         <v>0</v>
       </c>
       <c r="U348" s="19" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="V348" s="19" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="349" ht="20.1" customHeight="1" spans="1:22">
@@ -29220,7 +29112,7 @@
         <v>96001001</v>
       </c>
       <c r="B349" s="19" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C349" s="46"/>
       <c r="D349" s="28">
@@ -29275,10 +29167,10 @@
         <v>0</v>
       </c>
       <c r="U349" s="19" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="V349" s="19" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -29306,12 +29198,12 @@
   <sheetData>
     <row r="2" spans="2:23">
       <c r="B2" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="2:23">
       <c r="B3" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="2:23">
@@ -29322,16 +29214,16 @@
         <v>10010101</v>
       </c>
       <c r="F10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I10">
         <v>90090021</v>
       </c>
       <c r="J10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K10">
         <f>SUMIF(F:F,"="&amp;J10,G:G)</f>
@@ -29342,7 +29234,7 @@
         <v>自身速度提升50%,持续6秒</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="U10" s="3">
         <v>10010001</v>
@@ -29357,23 +29249,23 @@
         <v>10010102</v>
       </c>
       <c r="F11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I11">
         <v>90090041</v>
       </c>
       <c r="J11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" ref="N11:N66" si="0">VLOOKUP(J11,F:G,2,FALSE)</f>
         <v>增加被发现的概率,怪物发现距离+3</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="U11" s="3">
         <v>10010011</v>
@@ -29388,23 +29280,23 @@
         <v>10010103</v>
       </c>
       <c r="F12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G12" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I12">
         <v>90090061</v>
       </c>
       <c r="J12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身160攻击,持续20秒</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="U12" s="5">
         <v>10010103</v>
@@ -29428,7 +29320,7 @@
         <v>90090071</v>
       </c>
       <c r="J13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="0"/>
@@ -29450,23 +29342,23 @@
         <v>10010105</v>
       </c>
       <c r="F14" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I14">
         <v>90090091</v>
       </c>
       <c r="J14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="0"/>
         <v>攻击野兽类怪物,提升10%伤害</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="U14" s="5">
         <v>10010105</v>
@@ -29481,23 +29373,23 @@
         <v>10010106</v>
       </c>
       <c r="F15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I15">
         <v>90090101</v>
       </c>
       <c r="J15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
         <v>受到神圣属性的攻击降低10%伤害,持续30分钟</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="U15" s="5">
         <v>10010106</v>
@@ -29512,23 +29404,23 @@
         <v>10010107</v>
       </c>
       <c r="F16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G16" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I16">
         <v>90090111</v>
       </c>
       <c r="J16" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="0"/>
         <v>受到暗影属性的攻击降低10%伤害,持续30分钟</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U16" s="5">
         <v>10010107</v>
@@ -29543,23 +29435,23 @@
         <v>10010108</v>
       </c>
       <c r="F17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G17" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I17">
         <v>90090121</v>
       </c>
       <c r="J17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v>自身触发隐身效果,持续10秒</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="U17" s="5">
         <v>10010108</v>
@@ -29574,23 +29466,23 @@
         <v>10010109</v>
       </c>
       <c r="F18" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G18" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I18">
         <v>90090131</v>
       </c>
       <c r="J18" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v>自身幸运值+1,持续30分钟</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="U18" s="5">
         <v>10010109</v>
@@ -29605,23 +29497,23 @@
         <v>10010110</v>
       </c>
       <c r="F19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I19">
         <v>90090141</v>
       </c>
       <c r="J19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
         <v>攻击人形类怪物,提升10%伤害,持续30分钟</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U19" s="5">
         <v>10010110</v>
@@ -29636,23 +29528,23 @@
         <v>10010111</v>
       </c>
       <c r="F20" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G20" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I20">
         <v>90090151</v>
       </c>
       <c r="J20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v>受到冰霜属性的攻击降低10%伤害,持续30分钟</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="U20" s="5">
         <v>10010111</v>
@@ -29667,23 +29559,23 @@
         <v>10010112</v>
       </c>
       <c r="F21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I21">
         <v>90090161</v>
       </c>
       <c r="J21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="0"/>
         <v>受到火焰属性的攻击降低10%伤害,持续30分钟</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="U21" s="5">
         <v>10010112</v>
@@ -29698,23 +29590,23 @@
         <v>10010113</v>
       </c>
       <c r="F22" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G22" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I22">
         <v>90090171</v>
       </c>
       <c r="J22" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身300攻击,持续20秒</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="U22" s="5">
         <v>10010113</v>
@@ -29729,23 +29621,23 @@
         <v>10010114</v>
       </c>
       <c r="F23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G23" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="I23">
         <v>90090181</v>
       </c>
       <c r="J23" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身30%暴击概率，持续15秒</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="U23" s="5">
         <v>10010114</v>
@@ -29760,23 +29652,23 @@
         <v>10010201</v>
       </c>
       <c r="F24" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G24" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I24">
         <v>90090191</v>
       </c>
       <c r="J24" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v>攻击恶魔类怪物,提升10%伤害,持续30秒</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="U24" s="3">
         <v>10010002</v>
@@ -29791,23 +29683,23 @@
         <v>10010202</v>
       </c>
       <c r="F25" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G25" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I25">
         <v>90090201</v>
       </c>
       <c r="J25" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
         <v>受到闪电属性的攻击降低10%伤害,持续30分钟</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="U25" s="3">
         <v>10010012</v>
@@ -29822,19 +29714,19 @@
         <v>10010203</v>
       </c>
       <c r="F26" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G26" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I26">
         <v>90090211</v>
       </c>
       <c r="J26" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="U26" s="5">
         <v>10010203</v>
@@ -29849,23 +29741,23 @@
         <v>10010204</v>
       </c>
       <c r="F27" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G27" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="I27">
         <v>90090221</v>
       </c>
       <c r="J27" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N27" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身500攻击,持续20秒</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="U27" s="5">
         <v>10010204</v>
@@ -29880,23 +29772,23 @@
         <v>10010205</v>
       </c>
       <c r="F28" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G28" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I28">
         <v>91001011</v>
       </c>
       <c r="J28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="0"/>
         <v>每秒恢复50点血量,持续12秒</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="U28" s="5">
         <v>10010205</v>
@@ -29911,23 +29803,23 @@
         <v>10010206</v>
       </c>
       <c r="F29" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G29" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="I29">
         <v>91001031</v>
       </c>
       <c r="J29" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身100点攻击,持续15秒</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="U29" s="5">
         <v>10010206</v>
@@ -29942,10 +29834,10 @@
         <v>10010207</v>
       </c>
       <c r="F30" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G30" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I30">
         <v>91001041</v>
@@ -29958,7 +29850,7 @@
         <v>立即提升50点物防和魔防,持续15秒</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U30" s="5">
         <v>10010207</v>
@@ -29973,10 +29865,10 @@
         <v>10010208</v>
       </c>
       <c r="F31" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G31" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I31">
         <v>91001042</v>
@@ -29985,7 +29877,7 @@
         <v>76</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="U31" s="5">
         <v>10010208</v>
@@ -30000,23 +29892,23 @@
         <v>10010209</v>
       </c>
       <c r="F32" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G32" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I32">
         <v>91001061</v>
       </c>
       <c r="J32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N32" t="str">
         <f t="shared" si="0"/>
         <v>提高自身100点血量上限,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="U32" s="5">
         <v>10010209</v>
@@ -30031,23 +29923,23 @@
         <v>10010210</v>
       </c>
       <c r="F33" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G33" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I33">
         <v>91001071</v>
       </c>
       <c r="J33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N33" t="str">
         <f t="shared" si="0"/>
         <v>提高自身50点攻击,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="U33" s="5">
         <v>10010210</v>
@@ -30062,23 +29954,23 @@
         <v>10010211</v>
       </c>
       <c r="F34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I34">
         <v>91001081</v>
       </c>
       <c r="J34" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v>提升自身25点物防和魔防,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T34" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="U34" s="5">
         <v>10010211</v>
@@ -30093,10 +29985,10 @@
         <v>10010212</v>
       </c>
       <c r="F35" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G35" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I35">
         <v>91001082</v>
@@ -30105,7 +29997,7 @@
         <v>76</v>
       </c>
       <c r="T35" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="U35" s="5">
         <v>10010212</v>
@@ -30120,23 +30012,23 @@
         <v>10010213</v>
       </c>
       <c r="F36" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G36" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I36">
         <v>91002011</v>
       </c>
       <c r="J36" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N36" t="str">
         <f t="shared" si="0"/>
         <v>每秒恢复65点血量,持续12秒</v>
       </c>
       <c r="T36" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U36" s="5">
         <v>10010213</v>
@@ -30151,24 +30043,24 @@
         <v>10010214</v>
       </c>
       <c r="F37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G37" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I37">
         <f t="shared" ref="I37:I43" si="2">I29+1000</f>
         <v>91002031</v>
       </c>
       <c r="J37" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N37" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身140点攻击,持续15秒</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U37" s="5">
         <v>10010214</v>
@@ -30183,24 +30075,24 @@
         <v>10010301</v>
       </c>
       <c r="F38" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G38" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I38">
         <f t="shared" si="2"/>
         <v>91002041</v>
       </c>
       <c r="J38" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N38" t="str">
         <f t="shared" si="0"/>
         <v>立即提升70点物防和魔防,持续15秒</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="U38" s="3">
         <v>10010003</v>
@@ -30215,10 +30107,10 @@
         <v>10010302</v>
       </c>
       <c r="F39" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G39" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I39">
         <f t="shared" si="2"/>
@@ -30228,7 +30120,7 @@
         <v>76</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="U39" s="3">
         <v>10010013</v>
@@ -30243,24 +30135,24 @@
         <v>10010303</v>
       </c>
       <c r="F40" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G40" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I40">
         <f t="shared" si="2"/>
         <v>91002061</v>
       </c>
       <c r="J40" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N40" t="str">
         <f t="shared" si="0"/>
         <v>提高自身200点血量上限,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T40" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="U40" s="5">
         <v>10010303</v>
@@ -30275,24 +30167,24 @@
         <v>10010304</v>
       </c>
       <c r="F41" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G41" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I41">
         <f t="shared" si="2"/>
         <v>91002071</v>
       </c>
       <c r="J41" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N41" t="str">
         <f t="shared" si="0"/>
         <v>提高自身70点攻击,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T41" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="U41" s="5">
         <v>10010304</v>
@@ -30307,24 +30199,24 @@
         <v>10010305</v>
       </c>
       <c r="F42" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G42" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I42">
         <f t="shared" si="2"/>
         <v>91002081</v>
       </c>
       <c r="J42" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N42" t="str">
         <f t="shared" si="0"/>
         <v>提升自身35点物防和魔防,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="U42" s="5">
         <v>10010305</v>
@@ -30339,10 +30231,10 @@
         <v>10010306</v>
       </c>
       <c r="F43" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G43" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I43">
         <f t="shared" si="2"/>
@@ -30352,7 +30244,7 @@
         <v>76</v>
       </c>
       <c r="T43" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U43" s="5">
         <v>10010306</v>
@@ -30367,23 +30259,23 @@
         <v>10010307</v>
       </c>
       <c r="F44" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G44" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I44">
         <v>91003011</v>
       </c>
       <c r="J44" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N44" t="str">
         <f t="shared" si="0"/>
         <v>每秒恢复80点血量,持续12秒</v>
       </c>
       <c r="T44" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="U44" s="5">
         <v>10010307</v>
@@ -30398,24 +30290,24 @@
         <v>10010308</v>
       </c>
       <c r="F45" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G45" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I45">
         <f t="shared" ref="I45:I51" si="3">I37+1000</f>
         <v>91003031</v>
       </c>
       <c r="J45" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N45" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身180点攻击,持续15秒</v>
       </c>
       <c r="T45" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="U45" s="5">
         <v>10010308</v>
@@ -30430,24 +30322,24 @@
         <v>10010309</v>
       </c>
       <c r="F46" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G46" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I46">
         <f t="shared" si="3"/>
         <v>91003041</v>
       </c>
       <c r="J46" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N46" t="str">
         <f t="shared" si="0"/>
         <v>立即提升120点物防和魔防,持续15秒</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="U46" s="5">
         <v>10010309</v>
@@ -30462,10 +30354,10 @@
         <v>10010310</v>
       </c>
       <c r="F47" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G47" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I47">
         <f t="shared" si="3"/>
@@ -30475,7 +30367,7 @@
         <v>76</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U47" s="5">
         <v>10010310</v>
@@ -30490,24 +30382,24 @@
         <v>10010311</v>
       </c>
       <c r="F48" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G48" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I48">
         <f t="shared" si="3"/>
         <v>91003061</v>
       </c>
       <c r="J48" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N48" t="str">
         <f t="shared" si="0"/>
         <v>提高自身300点血量上限,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="U48" s="5">
         <v>10010311</v>
@@ -30522,24 +30414,24 @@
         <v>10010312</v>
       </c>
       <c r="F49" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I49">
         <f t="shared" si="3"/>
         <v>91003071</v>
       </c>
       <c r="J49" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N49" t="str">
         <f t="shared" si="0"/>
         <v>提高自身90点攻击,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T49" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="U49" s="5">
         <v>10010312</v>
@@ -30554,24 +30446,24 @@
         <v>10010313</v>
       </c>
       <c r="F50" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G50" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I50">
         <f t="shared" si="3"/>
         <v>91003081</v>
       </c>
       <c r="J50" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N50" t="str">
         <f t="shared" si="0"/>
         <v>提升自身45点物防和魔防,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T50" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U50" s="5">
         <v>10010313</v>
@@ -30586,10 +30478,10 @@
         <v>10010401</v>
       </c>
       <c r="F51" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G51" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I51">
         <f t="shared" si="3"/>
@@ -30599,7 +30491,7 @@
         <v>76</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="U51" s="3">
         <v>10010004</v>
@@ -30614,23 +30506,23 @@
         <v>10010402</v>
       </c>
       <c r="F52" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G52" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="I52">
         <v>91004011</v>
       </c>
       <c r="J52" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N52" t="str">
         <f t="shared" si="0"/>
         <v>每秒恢复95点血量,持续12秒</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="U52" s="3">
         <v>10010014</v>
@@ -30645,24 +30537,24 @@
         <v>10010403</v>
       </c>
       <c r="F53" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G53" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="I53">
         <f>I45+1000</f>
         <v>91004031</v>
       </c>
       <c r="J53" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N53" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身240点攻击,持续15秒</v>
       </c>
       <c r="T53" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="U53" s="5">
         <v>10010403</v>
@@ -30677,24 +30569,24 @@
         <v>10010404</v>
       </c>
       <c r="F54" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G54" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I54">
         <f t="shared" ref="I54:I59" si="4">I46+1000</f>
         <v>91004041</v>
       </c>
       <c r="J54" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N54" t="str">
         <f t="shared" si="0"/>
         <v>立即提升120点物防和魔防,持续15秒</v>
       </c>
       <c r="T54" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U54" s="5">
         <v>10010404</v>
@@ -30709,10 +30601,10 @@
         <v>10010405</v>
       </c>
       <c r="F55" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G55" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I55">
         <f t="shared" si="4"/>
@@ -30722,7 +30614,7 @@
         <v>76</v>
       </c>
       <c r="T55" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="U55" s="5">
         <v>10010405</v>
@@ -30737,24 +30629,24 @@
         <v>10010406</v>
       </c>
       <c r="F56" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G56" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I56">
         <f t="shared" si="4"/>
         <v>91004061</v>
       </c>
       <c r="J56" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N56" t="str">
         <f t="shared" si="0"/>
         <v>提高自身400点血量上限,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T56" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="U56" s="5">
         <v>10010406</v>
@@ -30769,24 +30661,24 @@
         <v>10010407</v>
       </c>
       <c r="F57" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G57" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I57">
         <f t="shared" si="4"/>
         <v>91004071</v>
       </c>
       <c r="J57" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N57" t="str">
         <f t="shared" si="0"/>
         <v>提高自身120点攻击,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T57" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="U57" s="5">
         <v>10010407</v>
@@ -30801,24 +30693,24 @@
         <v>10010408</v>
       </c>
       <c r="F58" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G58" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I58">
         <f t="shared" si="4"/>
         <v>91004081</v>
       </c>
       <c r="J58" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N58" t="str">
         <f t="shared" si="0"/>
         <v>提升自身60点物防和魔防,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T58" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="U58" s="5">
         <v>10010408</v>
@@ -30833,10 +30725,10 @@
         <v>10010409</v>
       </c>
       <c r="F59" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G59" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I59">
         <f t="shared" si="4"/>
@@ -30846,7 +30738,7 @@
         <v>76</v>
       </c>
       <c r="T59" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="U59" s="5">
         <v>10010409</v>
@@ -30861,23 +30753,23 @@
         <v>10010410</v>
       </c>
       <c r="F60" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G60" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I60">
         <v>91005011</v>
       </c>
       <c r="J60" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N60" t="str">
         <f t="shared" si="0"/>
         <v>每秒恢复120点血量,持续12秒</v>
       </c>
       <c r="T60" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U60" s="5">
         <v>10010410</v>
@@ -30892,24 +30784,24 @@
         <v>10010411</v>
       </c>
       <c r="F61" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G61" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I61">
         <f>I53+1000</f>
         <v>91005031</v>
       </c>
       <c r="J61" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N61" t="str">
         <f t="shared" si="0"/>
         <v>立即提升自身320点攻击,持续15秒</v>
       </c>
       <c r="T61" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="U61" s="5">
         <v>10010411</v>
@@ -30924,24 +30816,24 @@
         <v>10010501</v>
       </c>
       <c r="F62" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G62" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="I62">
         <f t="shared" ref="I62:I67" si="5">I54+1000</f>
         <v>91005041</v>
       </c>
       <c r="J62" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N62" t="str">
         <f t="shared" si="0"/>
         <v>立即提升160点物防和魔防,持续15秒</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="U62" s="3">
         <v>10010005</v>
@@ -30956,10 +30848,10 @@
         <v>10010502</v>
       </c>
       <c r="F63" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G63" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I63">
         <f t="shared" si="5"/>
@@ -30969,7 +30861,7 @@
         <v>76</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="U63" s="3">
         <v>10010015</v>
@@ -30984,24 +30876,24 @@
         <v>10010503</v>
       </c>
       <c r="F64" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G64" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I64">
         <f t="shared" si="5"/>
         <v>91005061</v>
       </c>
       <c r="J64" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N64" t="str">
         <f t="shared" si="0"/>
         <v>提高自身500点血量上限,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T64" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="U64" s="5">
         <v>10010503</v>
@@ -31016,24 +30908,24 @@
         <v>10010504</v>
       </c>
       <c r="F65" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G65" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I65">
         <f t="shared" si="5"/>
         <v>91005071</v>
       </c>
       <c r="J65" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N65" t="str">
         <f t="shared" si="0"/>
         <v>提高自身160点攻击,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T65" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="U65" s="5">
         <v>10010504</v>
@@ -31048,24 +30940,24 @@
         <v>10010505</v>
       </c>
       <c r="F66" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G66" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I66">
         <f t="shared" si="5"/>
         <v>91005081</v>
       </c>
       <c r="J66" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N66" t="str">
         <f t="shared" si="0"/>
         <v>提升自身80点物防和魔防,持续30分钟,玩家死亡后合剂效果消失</v>
       </c>
       <c r="T66" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="U66" s="5">
         <v>10010505</v>
@@ -31080,10 +30972,10 @@
         <v>10010506</v>
       </c>
       <c r="F67" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G67" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I67">
         <f t="shared" si="5"/>
@@ -31093,7 +30985,7 @@
         <v>76</v>
       </c>
       <c r="T67" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="U67" s="5">
         <v>10010506</v>
@@ -31108,13 +31000,13 @@
         <v>10010507</v>
       </c>
       <c r="F68" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G68" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="T68" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="U68" s="5">
         <v>10010507</v>
@@ -31125,13 +31017,13 @@
         <v>10010508</v>
       </c>
       <c r="F69" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G69" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="T69" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="U69" s="5">
         <v>10010508</v>
@@ -31142,13 +31034,13 @@
         <v>10010509</v>
       </c>
       <c r="F70" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G70" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T70" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="U70" s="5">
         <v>10010509</v>

--- a/S_数据表/SkillBuff_Template.xlsx
+++ b/S_数据表/SkillBuff_Template.xlsx
@@ -4562,6 +4562,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="方正书宋_GBK"/>
       <charset val="134"/>
@@ -4575,18 +4576,17 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="方正书宋_GBK"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6242,7 +6242,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{A3ED300F-653F-4B65-829F-6B446B7C29CF}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{CA634CF5-EC45-4898-A60E-D5180668819A}">
       <tableStyleElement type="wholeTable" dxfId="23"/>
       <tableStyleElement type="headerRow" dxfId="22"/>
     </tableStyle>
